--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_218_Ecuador_mainland.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_218_Ecuador_mainland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R598cdd9267fa4bd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb323f0301d1141c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra2ac69489fc8482f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R07b4fff67c7b4c37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf581108b01334f3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R7fcf9c87c7784873"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6b204635239f4053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R83a2aae631cf4559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rec065573572e4da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6297563076e74f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rc0077dea9404460c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R08142628178f4166"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ218CommercialTable" displayName="EEZ218CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ218CommercialTable" displayName="EEZ218CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ218FunctionalTable" displayName="EEZ218FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ218FunctionalTable" displayName="EEZ218FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ218ValidationTable" displayName="EEZ218ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ218ValidationTable" displayName="EEZ218ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6188,7 +6142,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd220f0cab8bb4cba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R734bd4d4c6fa4eda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6198,20 +6152,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6219,606 +6163,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>18557.760900953</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.470033451736964</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>29.51436553701575</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>18557.760900953</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>29.518590854184712</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$83,A2,'Species'!$U$2:$U$83))</x:f>
-        <x:v>547798.9512050179</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.470033451736964</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>29.51436553701575</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>547720.5387792655</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>78.41242575237993</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000143161375557</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00014316137555685235</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>7641.0429321230995</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.72509163066624</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>53.09964659800132</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>7641.0429321230995</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>53.188400852525994</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$83,A3,'Species'!$U$2:$U$83))</x:f>
-        <x:v>406414.854405124</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.72509163066624</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>53.09964659800132</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>405736.6793358924</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>678.1750692315982</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0016714660117534</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0016714660117533161</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>488.59315746</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.7618009494426294</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>577.8311488653759</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>488.59315746</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>579.9350414884118</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$83,A4,'Species'!$U$2:$U$83))</x:f>
-        <x:v>283352.2930425192</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.7618009494426294</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>577.8311488653759</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>282324.3455028733</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1027.9475396458874</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0036410162850635</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.003641016285063612</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>17272.185947</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.89</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>77.6247116628692</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>17272.185947</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>77.6247116628692</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$83,A5,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1340748.4539233367</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.89</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>77.6247116628692</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>1340748.4539233367</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.7037841310999999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.7037841310999999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$83,A6,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>7.037841310999999</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>7.037841310999999</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>43945.71636813059</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.561087714511406</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>363.98854351595213</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>43945.71636813059</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>687.1060863467762</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$83,A7,'Species'!$U$2:$U$83))</x:f>
-        <x:v>30195369.185411673</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.561087714511406</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>363.98854351595213</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>15995737.294600992</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>14199631.890810682</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.8877134969954434</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.8877134969954436</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>112031.10301835249</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.615177867732605</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>412.2663305062138</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>112031.10301835249</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>639.5379275063528</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$83,A8,'Species'!$U$2:$U$83))</x:f>
-        <x:v>71648139.44060786</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.615177867732605</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>412.2663305062138</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>46186651.743939795</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>25461487.696668066</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5512737281287965</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5512737281287964</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>9812.245469395999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4712767719722337</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>295.9898182136887</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>9812.245469395999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>296.643523884378</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$83,A9,'Species'!$U$2:$U$83))</x:f>
-        <x:v>2910739.073260152</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4712767719722337</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>295.9898182136887</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2904324.7527546124</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>6414.320505539421</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.002208541072914</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0022085410729140212</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13512.513327833498</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.425793264084734</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2665.589469803637</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13512.513327833498</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2792.9963882793</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$83,A10,'Species'!$U$2:$U$83))</x:f>
-        <x:v>37740400.92121486</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.425793264084734</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2665.589469803637</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>36018813.23725427</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1721587.6839605942</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.047796901930682</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.047796901930682034</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>4330.7317232155</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.426135719226639</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2667.6922016055223</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>4330.7317232155</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2669.769918598266</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$83,A11,'Species'!$U$2:$U$83))</x:f>
-        <x:v>11562057.280159974</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.426135719226639</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2667.6922016055223</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>11553059.245267635</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>8998.03489233926</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.000778844347745</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0007788443477449521</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1646a586dabb4afb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57e9d28bfbc34977"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6828,20 +6378,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6849,1200 +6389,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>8076.69059857</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.139665583862841</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1379.3217480187566</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>8076.69059857</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1379.3334828832449</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$83,A2,'Species'!$U$2:$U$83))</x:f>
-        <x:v>11140449.773495918</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.139665583862841</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1379.3217480187566</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>11140354.99462623</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>94.7788696885109</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000085077064182</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00000850770641817333</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3767</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3767</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$83,A3,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1086414.6672277923</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>1086414.6672277923</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>47.84</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.22</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1659.5869074375596</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>47.84</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1659.5869074375596</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$83,A4,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>79394.63765181285</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.22</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1659.5869074375596</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>79394.63765181285</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3793.4078753232</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.375286403738688</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2372.938068826615</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3793.4078753232</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2412.3486226047726</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$83,A5,'Species'!$U$2:$U$83))</x:f>
-        <x:v>9151022.263014019</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.375286403738688</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2372.938068826615</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>9001521.957941107</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>149500.30507291108</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0166083364314877</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.016608336431487843</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>33.4126766718</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>33.4126766718</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$83,A6,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>74801.66556130783</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>74801.66556130783</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>8962.6151387176</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.460121834583015</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2884.840686943604</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>8962.6151387176</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2896.6603342515705</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$83,A7,'Species'!$U$2:$U$83))</x:f>
-        <x:v>25961651.76348591</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.460121834583015</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2884.840686943604</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>25855716.813589223</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>105934.94989668578</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0040971577257145</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.004097157725714593</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>304.6453952081</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.565363029936936</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>367.58944281535275</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>304.6453952081</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>370.49174515566364</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$83,A8,'Species'!$U$2:$U$83))</x:f>
-        <x:v>112868.60412428582</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.565363029936936</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>367.58944281535275</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>111984.43108080843</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>884.1730434773926</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0078954997131644</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.007895499713164321</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>27.84</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>831.7637711026708</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>27.84</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$83,A9,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>23156.303387498356</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>23156.303387498356</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13200.555843138298</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.446102352979674</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2793.202055602727</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13200.555843138298</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2850.2249422778204</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$83,A10,'Species'!$U$2:$U$83))</x:f>
-        <x:v>37624553.516044</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.446102352979674</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2793.202055602727</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>36871819.71615248</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>752733.7998915166</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0204148806781501</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.020414880678150137</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>3.0429319229</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>39.810717055349734</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>3.0429319229</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$83,A11,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>121.14130180126318</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>121.14130180126318</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>9784.405469395999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.47</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>295.1209226666387</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>9784.405469395999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>295.1209226666387</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$83,A12,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2887582.7698726533</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.47</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>295.1209226666387</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>2887582.7698726533</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>31.3228251101</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>501.18723362727246</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>31.3228251101</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>501.18723362727246</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$83,A13,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>15698.600066321884</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.7</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>501.18723362727246</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>15698.600066321884</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>44186.9237386056</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.492605699460117</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>310.8892459137866</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>44186.9237386056</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>358.50351264982777</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$83,A14,'Species'!$U$2:$U$83))</x:f>
-        <x:v>15841167.373480167</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.492605699460117</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>310.8892459137866</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>13737239.40034509</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2103927.9731350765</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.1531550780924895</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.15315507809248954</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>75677.1308165821</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.5725277926922767</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>373.70403982148173</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>75677.1308165821</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>539.4560730364839</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$83,A15,'Species'!$U$2:$U$83))</x:f>
-        <x:v>40824487.80898166</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.5725277926922767</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>373.70403982148173</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>28280849.508255478</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>12543638.300726179</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.4435382429747932</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.4435382429747932</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>4642.6256137061</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.5019458406597614</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>317.6477918538784</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>4642.6256137061</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>636.4652925217601</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$83,A16,'Species'!$U$2:$U$83))</x:f>
-        <x:v>2954870.069296469</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.5019458406597614</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>317.6477918538784</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1474719.7745979996</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1480150.2946984693</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>2.0036824081388276</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>1.0036824081388276</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>11.2153495741</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.0004706389992686</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>10.010842737441102</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>11.2153495741</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>10.015613641997552</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$83,A17,'Species'!$U$2:$U$83))</x:f>
-        <x:v>112.3286081941274</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.0004706389992686</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>10.010842737441102</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>112.27510083174214</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0.053507362385261104</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0004765737192742</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0004765737192741281</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>7638.0000002002</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.7251414663976132</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>53.10574018580969</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>7638.0000002002</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>53.193730438946496</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$83,A18,'Species'!$U$2:$U$83))</x:f>
-        <x:v>406293.7131033227</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.7251414663976132</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>53.10574018580969</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>405621.64354984614</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>672.0695534765837</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0016568878021272</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0016568878021273395</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>3918.4030777999997</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.547433538464949</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>35.27228041396553</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>3918.4030777999997</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>37.30430210579095</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$83,A19,'Species'!$U$2:$U$83))</x:f>
-        <x:v>146173.2921865123</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.547433538464949</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>35.27228041396553</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>138211.0121351072</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>7962.280051405105</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0576095922343847</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.05760959223438459</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>42989.6140311221</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.8374203758497134</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>68.77338106823882</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>42989.6140311221</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>186.50728290532177</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$83,A20,'Species'!$U$2:$U$83))</x:f>
-        <x:v>8017876.10609308</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.8374203758497134</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>68.77338106823882</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>2956541.107738867</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>5061334.998354213</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>2.711910916816263</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>1.711910916816263</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>488.59315746</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.7618009494426294</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>577.8311488653759</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>488.59315746</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>579.9350414884118</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$83,A21,'Species'!$U$2:$U$83))</x:f>
-        <x:v>283352.2930425192</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.7618009494426294</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>577.8311488653759</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>282324.3455028733</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>1027.9475396458874</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0036410162850635</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.003641016285063612</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>7.3120894871</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.61</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>407.3802778041126</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>7.3120894871</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$83,A22,'Species'!$U$2:$U$83))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>2978.801046583329</x:v>
       </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.61</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>2978.801046583329</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a5349aa2aaf462f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cd589f53b1b4913"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8217,7 +6978,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8316,7 +7077,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>156635027.49107182</x:v>
+        <x:v>115235123.32919997</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8330,7 +7091,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>156635027.49107182</x:v>
+        <x:v>134427165.56673172</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8344,7 +7105,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.9802322387695312e-8</x:v>
+        <x:v>-41399904.16187188</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8358,7 +7119,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.9802322387695312e-8</x:v>
+        <x:v>-22207861.92434013</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8369,9 +7130,9 @@
         <x:v>EEZ_218</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8383,47 +7144,19 @@
         <x:v>EEZ_218</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_218</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_218</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra804637738674901"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b40048b0d4b4535"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8470,7 +7203,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
